--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_19_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_19_R2.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1683</v>
+        <v>6.3609</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5542</v>
+        <v>4.7468</v>
       </c>
       <c r="F2" t="n">
         <v>1.6141</v>
@@ -610,10 +610,10 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3145</v>
+        <v>0.5072</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2794</v>
+        <v>0.472</v>
       </c>
       <c r="U2" t="n">
         <v>0.0351</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0804</v>
+        <v>5.3328</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2575</v>
+        <v>5.3754</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.177</v>
+        <v>-0.0426</v>
       </c>
       <c r="G3" t="n">
         <v>4.3007</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0659</v>
+        <v>0.3183</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0158</v>
+        <v>0.1338</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0501</v>
+        <v>0.1845</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.967</v>
+        <v>3.8592</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8126</v>
+        <v>4.4024</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8456</v>
+        <v>-0.5431</v>
       </c>
       <c r="G4" t="n">
         <v>5.2501</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4274</v>
+        <v>0.4648</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0589</v>
+        <v>0.5309</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3686</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5888</v>
+        <v>2.942</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4281</v>
+        <v>4.5461</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8394</v>
+        <v>-1.6041</v>
       </c>
       <c r="G5" t="n">
         <v>0.7249</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3457</v>
+        <v>0.6989</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7433</v>
+        <v>0.8612</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3976</v>
+        <v>-0.1623</v>
       </c>
       <c r="V5" t="n">
         <v>1.7501</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1847</v>
+        <v>1.5956</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0464</v>
+        <v>-0.4002</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2311</v>
+        <v>1.9958</v>
       </c>
       <c r="G6" t="n">
         <v>0.9302</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1128</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5623</v>
+        <v>0.2084</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5505</v>
+        <v>0.3152</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5567</v>
+        <v>0.5299</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2073</v>
+        <v>0.0461</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3494</v>
+        <v>0.4838</v>
       </c>
       <c r="G7" t="n">
         <v>1.6011</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6361</v>
+        <v>0.6093</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4876</v>
+        <v>0.3264</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1485</v>
+        <v>0.2829</v>
       </c>
       <c r="V7" t="n">
         <v>-2.1444</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4672</v>
+        <v>0.3386</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1922</v>
+        <v>-0.2315</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2751</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.7818</v>
+        <v>0.0672</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9148</v>
+        <v>0.6963</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.867</v>
+        <v>-0.6291</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7479</v>
+        <v>-0.7191</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1456</v>
+        <v>0.0672</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.7863</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0339</v>
+        <v>0.7863</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7692</v>
+        <v>0.6291</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2647</v>
+        <v>0.1573</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>3.481</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7957</v>
+        <v>0.4876</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6853</v>
+        <v>0.1601</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3722</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2315</v>
+        <v>-0.021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6037</v>
+        <v>0.012</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0672</v>
+        <v>-0.6772</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6963</v>
+        <v>-0.3659</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6291</v>
+        <v>-0.3113</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7191</v>
+        <v>-0.1155</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0672</v>
+        <v>0.4033</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7863</v>
+        <v>-0.5188</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7863</v>
+        <v>-0.5617</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6291</v>
+        <v>-0.7692</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>0.2075</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6814</v>
+        <v>-0.2596</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4876</v>
+        <v>0.0944</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1937</v>
+        <v>-0.3541</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0507</v>
+        <v>-0.4108</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3316</v>
+        <v>1.1108</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2809</v>
+        <v>-1.5216</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6772</v>
+        <v>-1.8354</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3659</v>
+        <v>0.3662</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3113</v>
+        <v>-2.2016</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1155</v>
+        <v>-0.0339</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4033</v>
+        <v>1.4284</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5188</v>
+        <v>-1.4623</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5617</v>
+        <v>-1.8016</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7692</v>
+        <v>-1.0622</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2075</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3014</v>
+        <v>0.6565</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2161</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0852</v>
+        <v>-0.0395</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3346</v>
+        <v>-1.0991</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9181</v>
+        <v>-1.1053</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2527</v>
+        <v>0.0062</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8354</v>
+        <v>-3.7818</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3662</v>
+        <v>-1.9148</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2016</v>
+        <v>-1.867</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0339</v>
+        <v>-1.7479</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4284</v>
+        <v>-1.1456</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4623</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8016</v>
+        <v>-2.0339</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0622</v>
+        <v>-0.7692</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.2647</v>
       </c>
       <c r="P11" t="n">
         <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7328</v>
+        <v>1.9147</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5034</v>
+        <v>1.4982</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2293</v>
+        <v>0.4165</v>
       </c>
       <c r="V11" t="n">
         <v>0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2911</v>
+        <v>-4.0387</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3139</v>
+        <v>-3.196</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9772</v>
+        <v>-0.8427</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4169</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8602</v>
+        <v>1.1125</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4367</v>
+        <v>0.5546</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4235</v>
+        <v>0.5579</v>
       </c>
       <c r="V12" t="n">
         <v>-1.719</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5237</v>
+        <v>-4.8428</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1134</v>
+        <v>-3.5669</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4103</v>
+        <v>-1.2759</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4407</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.3145</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2161</v>
+        <v>0.3304</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7793</v>
+        <v>-0.6449</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5361</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1852</v>
+        <v>10.5586</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3332</v>
+        <v>11.7067</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1479</v>
+        <v>-1.148</v>
       </c>
       <c r="G14" t="n">
-        <v>9.666100000000002</v>
+        <v>9.666099999999998</v>
       </c>
       <c r="H14" t="n">
         <v>4.664300000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>5.001900000000001</v>
+        <v>5.0019</v>
       </c>
       <c r="J14" t="n">
         <v>19.5525</v>
@@ -1525,7 +1525,7 @@
         <v>11.6239</v>
       </c>
       <c r="L14" t="n">
-        <v>7.928900000000001</v>
+        <v>7.928900000000004</v>
       </c>
       <c r="M14" t="n">
         <v>-9.886700000000001</v>
@@ -1546,13 +1546,13 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>6.5061</v>
+        <v>6.8795</v>
       </c>
       <c r="T14" t="n">
-        <v>5.8207</v>
+        <v>6.194</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6852999999999999</v>
+        <v>0.6852999999999998</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5076</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8807</v>
+        <v>2.5833</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6132</v>
+        <v>1.2594</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2674</v>
+        <v>1.3239</v>
       </c>
       <c r="G15" t="n">
         <v>0.7805</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.2153</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5623</v>
+        <v>0.2084</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4802</v>
+        <v>-0.4237</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8885</v>
+        <v>1.3124</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6699</v>
+        <v>3.5074</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2186</v>
+        <v>-2.195</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6796</v>
+        <v>0.9188</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6663</v>
+        <v>0.9389</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0133</v>
+        <v>-0.0201</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3212</v>
+        <v>4.1215</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4684</v>
+        <v>2.8736</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1472</v>
+        <v>1.2479</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3584</v>
+        <v>-3.2027</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1979</v>
+        <v>-1.9348</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1605</v>
+        <v>-1.2679</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1042</v>
+        <v>-0.6939</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9189</v>
+        <v>-0.5265</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1854</v>
+        <v>-0.1674</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
         <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6656</v>
+        <v>0.6926</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1536</v>
+        <v>0.6083</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.488</v>
+        <v>0.0842</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9188</v>
+        <v>-2.6796</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9389</v>
+        <v>-2.6663</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0201</v>
+        <v>-0.0133</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1215</v>
+        <v>-1.3212</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8736</v>
+        <v>-1.4684</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2479</v>
+        <v>0.1472</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2027</v>
+        <v>-1.3584</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9348</v>
+        <v>-1.1979</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2679</v>
+        <v>-0.1605</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3407</v>
+        <v>0.9082</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8804</v>
+        <v>0.8573</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4604</v>
+        <v>0.051</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1728</v>
+        <v>0.5629</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4783</v>
+        <v>0.4249</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6511</v>
+        <v>0.1379</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.252</v>
+        <v>1.6786</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.917</v>
+        <v>1.5714</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.335</v>
+        <v>0.1071</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5538</v>
+        <v>4.0415</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3564</v>
+        <v>2.8771</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9102</v>
+        <v>1.1643</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6982</v>
+        <v>-2.3629</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2734</v>
+        <v>-1.3057</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4248</v>
+        <v>-1.0572</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>3.0154</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9208</v>
+        <v>-0.51</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8804</v>
+        <v>-0.1373</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0404</v>
+        <v>-0.3727</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6083</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3852</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5429</v>
+        <v>0.8708</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.928</v>
+        <v>-0.3481</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6786</v>
+        <v>-1.1664</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5714</v>
+        <v>-0.2797</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1071</v>
+        <v>-0.8867</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0415</v>
+        <v>-0.237</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8771</v>
+        <v>0.1211</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1643</v>
+        <v>-0.3581</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3629</v>
+        <v>-0.9294</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3057</v>
+        <v>-0.4008</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0572</v>
+        <v>-0.5286</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.458</v>
+        <v>-0.2388</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0193</v>
+        <v>0.0356</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4387</v>
+        <v>-0.2743</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5165</v>
+        <v>0.0188</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7348</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2513</v>
+        <v>-0.6954</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2548</v>
+        <v>-2.252</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4922</v>
+        <v>-0.917</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7469</v>
+        <v>-1.335</v>
       </c>
       <c r="J20" t="n">
-        <v>1.633</v>
+        <v>-0.5538</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2722</v>
+        <v>0.3564</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6391</v>
+        <v>-0.9102</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8878</v>
+        <v>-1.6982</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.78</v>
+        <v>-1.2734</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1078</v>
+        <v>-0.4248</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2643</v>
+        <v>-0.7292</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0272</v>
+        <v>-0.6445</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2371</v>
+        <v>-0.0848</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0026</v>
+        <v>1.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6805</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6676</v>
+        <v>-0.0561</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1631</v>
+        <v>1.4989</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8307</v>
+        <v>-1.555</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1664</v>
+        <v>-1.2548</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2797</v>
+        <v>1.4922</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8867</v>
+        <v>-2.7469</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.237</v>
+        <v>1.633</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1211</v>
+        <v>2.2722</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3581</v>
+        <v>-0.6391</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9294</v>
+        <v>-2.8878</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4008</v>
+        <v>-0.78</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5286</v>
+        <v>-2.1078</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.429</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6721</v>
+        <v>-0.2631</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7569</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5361</v>
+        <v>2.0026</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4246</v>
+        <v>-1.2777</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1924</v>
+        <v>0.2612</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.617</v>
+        <v>-1.5388</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5861</v>
+        <v>0.987</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1646</v>
+        <v>1.4823</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4216</v>
+        <v>-0.4953</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0035</v>
+        <v>3.9039</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0035</v>
+        <v>3.5528</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.3511</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5896</v>
+        <v>-2.9169</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.168</v>
+        <v>-2.0705</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4216</v>
+        <v>-0.8464</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.0154</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3935</v>
+        <v>-1.4271</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3486</v>
+        <v>-0.4676</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0448</v>
+        <v>-0.9594</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2378</v>
+        <v>-2.0651</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0927</v>
+        <v>-0.5153</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1451</v>
+        <v>-1.5498</v>
       </c>
       <c r="G24" t="n">
-        <v>0.987</v>
+        <v>-0.5861</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4823</v>
+        <v>-0.1646</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4953</v>
+        <v>-0.4216</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9039</v>
+        <v>0.0035</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5528</v>
+        <v>0.0035</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3511</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.9169</v>
+        <v>-0.5896</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.0705</v>
+        <v>-0.168</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8464</v>
+        <v>-0.4216</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.7112</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>3.0154</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.3872</v>
+        <v>0.753</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8215</v>
+        <v>0.6409</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5657</v>
+        <v>0.112</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3394</v>
+        <v>-2.373</v>
       </c>
       <c r="E25" t="n">
         <v>-1.3879</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9514</v>
+        <v>-0.9851</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6419</v>
@@ -2404,13 +2404,13 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0892</v>
+        <v>-0.1228</v>
       </c>
       <c r="T25" t="n">
         <v>0.1142</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2034</v>
+        <v>-0.237</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.3165</v>
+        <v>-5.4008</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.5278</v>
+        <v>-4.7021</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7887</v>
+        <v>-0.6986</v>
       </c>
       <c r="G26" t="n">
         <v>-4.2822</v>
@@ -2482,13 +2482,13 @@
         <v>1.6237</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1967</v>
+        <v>-0.2809</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3285</v>
+        <v>-0.5028</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1318</v>
+        <v>0.2219</v>
       </c>
       <c r="V26" t="n">
         <v>-0.1418</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.1854</v>
+        <v>-7.039800000000001</v>
       </c>
       <c r="E27" t="n">
         <v>1.148099999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.3333</v>
+        <v>-8.187800000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-9.6661</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.6642</v>
+        <v>-4.664200000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-5.001900000000001</v>
@@ -2536,7 +2536,7 @@
         <v>9.886600000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>6.9596</v>
+        <v>6.959600000000002</v>
       </c>
       <c r="L27" t="n">
         <v>2.9269</v>
@@ -2551,7 +2551,7 @@
         <v>-7.9287</v>
       </c>
       <c r="P27" t="n">
-        <v>3.479199999999999</v>
+        <v>3.479200000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-16.2368</v>
@@ -2560,13 +2560,13 @@
         <v>19.7161</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.506099999999999</v>
+        <v>-3.3607</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6853999999999996</v>
+        <v>-0.6853999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.8208</v>
+        <v>-2.6752</v>
       </c>
       <c r="V27" t="n">
         <v>2.5076</v>
